--- a/results/Int Task Remove ACC -0.2/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_9_permute.xlsx
@@ -440,727 +440,727 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5573997015740916</v>
+        <v>0.5758275014185739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5573997015740916</v>
+        <v>0.584292709581153</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5551594056700923</v>
+        <v>0.5895698043418869</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5633766261059622</v>
+        <v>0.5947722926255175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5572252695290334</v>
+        <v>0.5868293298026606</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5589328121387891</v>
+        <v>0.5865393102578652</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.564477859739823</v>
+        <v>0.5668999432570456</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5604428052035391</v>
+        <v>0.5668999432570456</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5622039383813546</v>
+        <v>0.5686768383666435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5567902402118403</v>
+        <v>0.5655244520101717</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5598827312275392</v>
+        <v>0.5785280457306181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5589821995250405</v>
+        <v>0.5708908643843389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5602000714540907</v>
+        <v>0.5708908643843389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5731889540382069</v>
+        <v>0.567016581552235</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5755763613055083</v>
+        <v>0.5699367421137801</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.535969779122796</v>
+        <v>0.5712334237017422</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5364394846899103</v>
+        <v>0.5702530315448795</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5364394846899103</v>
+        <v>0.5693094172288422</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5341781728768678</v>
+        <v>0.5683395330265011</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5310625643612215</v>
+        <v>0.5698778975684593</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5304089695899796</v>
+        <v>0.5698778975684593</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5302534518630604</v>
+        <v>0.5698778975684593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5444055650127146</v>
+        <v>0.5627881806527542</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5609839648614001</v>
+        <v>0.5534844377193535</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5531029989702205</v>
+        <v>0.5508648046571254</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5732488493789799</v>
+        <v>0.555719479646092</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.573269865288023</v>
+        <v>0.5553769203286888</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5726162705167812</v>
+        <v>0.5489355442069647</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5830748376521027</v>
+        <v>0.5370815207111783</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.565807115986802</v>
+        <v>0.5494367736376436</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5618172456549608</v>
+        <v>0.5576287749826618</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5657598301914549</v>
+        <v>0.5641983481495492</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5479551520501019</v>
+        <v>0.5540875943088919</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5589548788432843</v>
+        <v>0.551784250677763</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5586228274804026</v>
+        <v>0.5512746148834669</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5529464304478491</v>
+        <v>0.5469894710295694</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5546171952167791</v>
+        <v>0.5737563835823718</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5494483323876174</v>
+        <v>0.5753693546014333</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5494483323876174</v>
+        <v>0.5756908980097935</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5296082634554358</v>
+        <v>0.569682449614358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5193514490469285</v>
+        <v>0.5698369165458252</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4913340899060589</v>
+        <v>0.5610921967929723</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5182859424584411</v>
+        <v>0.5614463148603492</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5301189500451842</v>
+        <v>0.5612151398608747</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5252380051699136</v>
+        <v>0.5666120253031545</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5253115608515646</v>
+        <v>0.5694102935922494</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5253115608515646</v>
+        <v>0.5890023747977219</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5256383582371855</v>
+        <v>0.5846163545804174</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5225437656305824</v>
+        <v>0.5765514994851102</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5252043797154446</v>
+        <v>0.572735010402875</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5220740600634681</v>
+        <v>0.5816384002690036</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5220740600634681</v>
+        <v>0.5816384002690036</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5141825862177668</v>
+        <v>0.5951327154656074</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5122543765630583</v>
+        <v>0.5951327154656074</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5573461110060316</v>
+        <v>0.5754880944875271</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5583054872538511</v>
+        <v>0.5742334447176513</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.545450055692159</v>
+        <v>0.5696141479099679</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5648803143979992</v>
+        <v>0.5729630330159932</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5648803143979992</v>
+        <v>0.5552897043061598</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5693861252968497</v>
+        <v>0.5552897043061598</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5693861252968497</v>
+        <v>0.5605184624760944</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5776884601643444</v>
+        <v>0.558879221570729</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5752474623289831</v>
+        <v>0.5628827522434483</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5338345627640124</v>
+        <v>0.5697454973414875</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5507586743164575</v>
+        <v>0.5224891242670702</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5563299918037955</v>
+        <v>0.5264789945989113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5285375028896875</v>
+        <v>0.5327459386755774</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5229315091524284</v>
+        <v>0.5389918668432003</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.530732614589244</v>
+        <v>0.5436973288779606</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5081730870268794</v>
+        <v>0.5318002227686358</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5079934010045605</v>
+        <v>0.5248954458525104</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5348853582161697</v>
+        <v>0.5170806800748167</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5005842422713994</v>
+        <v>0.5159594813273648</v>
       </c>
     </row>
     <row r="75">
@@ -1170,157 +1170,157 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.506854338734422</v>
+        <v>0.5133871340604839</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4944770191034613</v>
+        <v>0.516027783031755</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5025996679486371</v>
+        <v>0.5074680032784818</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4907361872937814</v>
+        <v>0.5058655402139419</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4913897820650232</v>
+        <v>0.4997677742050732</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.491094508542967</v>
+        <v>0.4984763465943719</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4985225815942669</v>
+        <v>0.4997362503415085</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4913645629741714</v>
+        <v>0.4997415043187693</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4943635331946283</v>
+        <v>0.4997625202278124</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4872317844608369</v>
+        <v>0.4993884370468444</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4940535485362419</v>
+        <v>0.4993674211378013</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4979278313683458</v>
+        <v>0.5000105079545216</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4979278313683458</v>
+        <v>0.5000105079545216</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5006798646575458</v>
+        <v>0.5000105079545216</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5013492213605699</v>
+        <v>0.5000105079545216</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5013597293150915</v>
+        <v>0.4987138263665595</v>
       </c>
     </row>
   </sheetData>
